--- a/QUẢN LÝ NHÂN SỰ/Nhân viên/Nam đảo/SUN HOÀNG GIANG/HÓA ĐƠN/TIỀN ĐIỆN T2 2026 TRƯƠNG HOÀNG GIANG.xlsx
+++ b/QUẢN LÝ NHÂN SỰ/Nhân viên/Nam đảo/SUN HOÀNG GIANG/HÓA ĐƠN/TIỀN ĐIỆN T2 2026 TRƯƠNG HOÀNG GIANG.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE52BBF6-6CED-4E73-A0D5-C4A9BB6F64C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DFBCB67-179F-49C9-BBBD-9974D24FD284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>CÔNG TY TNHH MTV VẬN TẢI VÀ DU LỊCH MINH HẢI</t>
   </si>
@@ -117,6 +117,9 @@
   </si>
   <si>
     <t>Phone: 0329630430</t>
+  </si>
+  <si>
+    <t>Đã đóng + doanh thu</t>
   </si>
 </sst>
 </file>
@@ -404,6 +407,9 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -436,9 +442,6 @@
           <color indexed="64"/>
         </bottom>
       </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -644,6 +647,55 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>360160</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{325A1204-5C62-FAF4-975E-829190D20F0A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10353675" y="1819275"/>
+          <a:ext cx="1866900" cy="4151110"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Invoice" displayName="Invoice" ref="B12:D17" totalsRowCount="1">
   <autoFilter ref="B12:D16" xr:uid="{00000000-0009-0000-0100-000001000000}">
@@ -653,8 +705,8 @@
   </autoFilter>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="NỘI DUNG" dataDxfId="4" dataCellStyle="Description"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="SỐ LƯỢNG " totalsRowLabel=" TỔNG CHI PHÍ TRỪ " dataDxfId="3" totalsRowDxfId="1" dataCellStyle="Description"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="TỔNG SỐ" dataDxfId="2" totalsRowDxfId="0" dataCellStyle="Currency"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="SỐ LƯỢNG " totalsRowLabel=" TỔNG CHI PHÍ TRỪ " dataDxfId="3" totalsRowDxfId="2" dataCellStyle="Description"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="TỔNG SỐ" dataDxfId="1" totalsRowDxfId="0" dataCellStyle="Currency"/>
   </tableColumns>
   <tableStyleInfo name="Invoice that calculates total" showFirstColumn="0" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -1165,13 +1217,14 @@
       <c r="D16" s="9"/>
       <c r="F16" s="12"/>
     </row>
-    <row r="17" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C17" s="14" t="s">
         <v>8</v>
       </c>
       <c r="D17" s="20"/>
-    </row>
-    <row r="18" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F17" s="12"/>
+    </row>
+    <row r="18" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C18" s="14" t="s">
         <v>12</v>
       </c>
@@ -1179,8 +1232,11 @@
         <f>SUBTOTAL(109,Invoice[TỔNG SỐ])</f>
         <v>35000</v>
       </c>
-    </row>
-    <row r="19" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F18" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="21" t="str">
         <f>Company_Name&amp;""</f>
         <v>CÔNG TY TNHH MTV VẬN TẢI VÀ DU LỊCH MINH HẢI</v>
@@ -1188,17 +1244,17 @@
       <c r="C19" s="21"/>
       <c r="D19" s="21"/>
     </row>
-    <row r="20" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="21"/>
       <c r="C20" s="21"/>
       <c r="D20" s="21"/>
     </row>
-    <row r="21" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="22"/>
       <c r="C21" s="22"/>
       <c r="D21" s="22"/>
     </row>
-    <row r="25" spans="2:4" ht="5.45" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="2:6" ht="5.45" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B20:D20"/>
@@ -1236,13 +1292,23 @@
   <headerFooter differentFirst="1">
     <oddFooter>Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
+  <drawing r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="26" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac37c1753acd5e330d2062ccec26ea66">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3b340c7101c92c5120abd06486f94548" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -1542,15 +1608,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1572,6 +1629,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69C393F6-8D9A-4F59-A33D-C9C2FA7EFF8E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{565030E0-6AB1-4C95-ADA8-2C257F6CE35D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1592,14 +1657,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69C393F6-8D9A-4F59-A33D-C9C2FA7EFF8E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B8768FD-A897-4E96-A3F0-B7D93590B1CF}">
   <ds:schemaRefs>

--- a/QUẢN LÝ NHÂN SỰ/Nhân viên/Nam đảo/SUN HOÀNG GIANG/HÓA ĐƠN/TIỀN ĐIỆN T2 2026 TRƯƠNG HOÀNG GIANG.xlsx
+++ b/QUẢN LÝ NHÂN SỰ/Nhân viên/Nam đảo/SUN HOÀNG GIANG/HÓA ĐƠN/TIỀN ĐIỆN T2 2026 TRƯƠNG HOÀNG GIANG.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DFBCB67-179F-49C9-BBBD-9974D24FD284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{371D6719-4899-4747-BCA4-56087974F92A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1309,6 +1309,26 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="26" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac37c1753acd5e330d2062ccec26ea66">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3b340c7101c92c5120abd06486f94548" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -1608,26 +1628,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69C393F6-8D9A-4F59-A33D-C9C2FA7EFF8E}">
   <ds:schemaRefs>
@@ -1637,6 +1637,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B8768FD-A897-4E96-A3F0-B7D93590B1CF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{565030E0-6AB1-4C95-ADA8-2C257F6CE35D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1655,16 +1667,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B8768FD-A897-4E96-A3F0-B7D93590B1CF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>